--- a/Updated_Test_Cases_Voucher.xlsx
+++ b/Updated_Test_Cases_Voucher.xlsx
@@ -973,21 +973,21 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>285750</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="13716000" cy="1692706"/>
+    <xdr:ext cx="9525000" cy="1175490"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="a9362501-87af-4ade-a449-50dea99717d8"/>
+        <xdr:cNvPr id="1" name="950e652c-7151-4375-8387-cdf9aaf65e47"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rde7e338fbe1041f7"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R30b651f9e4854ab7"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1000,21 +1000,21 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>1857375</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="13716000" cy="2225156"/>
+    <xdr:ext cx="9525000" cy="1545247"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="01400869-84fd-4e0d-a43f-74918ae47f78"/>
+        <xdr:cNvPr id="2" name="f04f6c8b-4b2d-4b66-8646-19f783116c8f"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R986663e1f5de470e"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rb876784b4c46422a"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1027,21 +1027,21 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>285750</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="13716000" cy="1647225"/>
+    <xdr:ext cx="9525000" cy="1143906"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="ea6d2a41-95eb-4526-9d61-3e8f42af4566"/>
+        <xdr:cNvPr id="3" name="be755087-6427-4018-847c-a92c72fb9835"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R1887054f427e485b"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R410ff990ca82453b"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1054,21 +1054,21 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>1857375</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="13716000" cy="1989167"/>
+    <xdr:ext cx="9525000" cy="1381366"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="0f6bc4b2-dc4c-4c29-a6e0-9790f286f048"/>
+        <xdr:cNvPr id="4" name="e97cac81-a6ca-4e5d-ab78-0ff154960853"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rd845177b337b4f8f"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rdcb76f2e7b5344e2"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -2422,7 +2422,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
@@ -2432,6 +2432,7 @@
     <col min="8" max="8" width="13.7109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="110.28515625" customWidth="1"/>
     <col min="11" max="11" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="150" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="23.25" x14ac:dyDescent="0.35">
@@ -2479,7 +2480,7 @@
       <c r="J3" s="20"/>
       <c r="K3" s="20"/>
     </row>
-    <row r="4" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A4" s="18" t="s">
         <v>1</v>
       </c>
@@ -2513,8 +2514,13 @@
       <c r="K4" s="18" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" ht="293.25" x14ac:dyDescent="0.25">
+      <c r="L4" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Screenshot</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="293.25" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>10</v>
       </c>
@@ -2562,12 +2568,13 @@
         <is>
           <t xml:space="preserve">Input: INV_433916_0110.txt
 Outputs: Settlement File_30092026.xlsx and VC Settlement Voucher On.30.09.2026.xlsx
-Evidence: Screenshots 1 and 2 below.</t>
+Evidence: See Screenshot column.</t>
         </is>
       </c>
       <c r="K5" s="4"/>
-    </row>
-    <row r="6" spans="1:11" ht="318.75" x14ac:dyDescent="0.25">
+      <c r="L5" s="3"/>
+    </row>
+    <row r="6" spans="1:12" ht="318.75" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>11</v>
       </c>
@@ -2601,22 +2608,33 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Retest
-required.</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>103</v>
+          <t xml:space="preserve">File
+rejected.
+Error
+reported.
+No voucher
+created.</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Passed</t>
+        </is>
       </c>
       <c r="J6" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scenario corrected to cover an unsupported format. TXT and legacy Notepad files are supported.
-Existing Not Passed status retained. A new negative-test result is required.</t>
+          <t xml:space="preserve">Robo rejected the unsupported file as expected.
+No voucher was generated.</t>
         </is>
       </c>
       <c r="K6" s="2"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25" ht="293.25" customHeight="1">
+      <c r="L6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No screenshot provided.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25" ht="293.25" customHeight="1">
       <c r="A7" s="8" t="s">
         <v>12</v>
       </c>
@@ -2671,12 +2689,13 @@
         <is>
           <t xml:space="preserve">Input: INV1309 (legacy Notepad file, no extension shown)
 Outputs: Settlement File_12092026.xlsx and VC Settlement Voucher On.12.09.2026.xlsx
-Evidence: Screenshots 3 and 4 below.</t>
+Evidence: See Screenshot column.</t>
         </is>
       </c>
       <c r="K7" s="2"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25" ht="293.25" customHeight="1">
+      <c r="L7" s="1"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25" ht="293.25" customHeight="1">
       <c r="A8" s="8" t="s">
         <v>13</v>
       </c>
@@ -2714,24 +2733,30 @@
       </c>
       <c r="H8" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Awaiting
-result.</t>
+          <t xml:space="preserve">TXT file
+processed.
+ATM voucher
+generated.</t>
         </is>
       </c>
       <c r="I8" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Passed</t>
         </is>
       </c>
       <c r="J8" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ATM Acquirer execution result and output evidence are required.
-The supplied screenshots show VISA Settlement only.</t>
+          <t xml:space="preserve">ATM Acquirer Voucher generated successfully.</t>
         </is>
       </c>
       <c r="K8" s="2"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25" ht="293.25" customHeight="1">
+      <c r="L8" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No screenshot provided.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25" ht="293.25" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
@@ -2771,24 +2796,31 @@
       </c>
       <c r="H9" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Awaiting
-result.</t>
+          <t xml:space="preserve">Notepad
+file
+processed.
+ATM voucher
+generated.</t>
         </is>
       </c>
       <c r="I9" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pending</t>
+          <t xml:space="preserve">Passed</t>
         </is>
       </c>
       <c r="J9" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ATM Acquirer execution result and output evidence are required.
-The supplied screenshots show VISA Settlement only.</t>
+          <t xml:space="preserve">ATM Acquirer Voucher generated successfully.</t>
         </is>
       </c>
       <c r="K9" s="2"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L9" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No screenshot provided.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="8"/>
       <c r="B10" s="8"/>
       <c r="C10" s="9"/>
@@ -2800,8 +2832,9 @@
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
       <c r="K10" s="2"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L10" s="1"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="8"/>
       <c r="B11" s="8"/>
       <c r="C11" s="9"/>
@@ -2813,8 +2846,9 @@
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="K11" s="2"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L11" s="1"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="8"/>
       <c r="B12" s="8"/>
       <c r="C12" s="9"/>
@@ -2826,8 +2860,9 @@
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
       <c r="K12" s="2"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L12" s="1"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="8"/>
       <c r="B13" s="8"/>
       <c r="C13" s="9"/>
@@ -2839,101 +2874,13 @@
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
       <c r="K13" s="2"/>
-    </row>
-    <row r="15" spans="1:11" ht="24" customHeight="1">
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">INV file processing - execution evidence</t>
-        </is>
-      </c>
-      <c r="C15" s="18"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="18"/>
-      <c r="H15" s="18"/>
-      <c r="I15" s="18"/>
-      <c r="J15" s="18"/>
-      <c r="K15" s="18"/>
-    </row>
-    <row r="17" spans="1:11" ht="24" customHeight="1">
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. TXT input - TC 1</t>
-        </is>
-      </c>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
-      <c r="I17" s="5"/>
-      <c r="J17" s="5"/>
-      <c r="K17" s="5"/>
-    </row>
-    <row r="18" spans="1:11" ht="142.28390502929688" customHeight="1"/>
-    <row r="20" spans="1:11" ht="24" customHeight="1">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2. TXT output - TC 1</t>
-        </is>
-      </c>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
-      <c r="H20" s="5"/>
-      <c r="I20" s="5"/>
-      <c r="J20" s="5"/>
-      <c r="K20" s="5"/>
-    </row>
-    <row r="21" spans="1:11" ht="184.20912170410156" customHeight="1"/>
-    <row r="23" spans="1:11" ht="24" customHeight="1">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3. Notepad input - TC 3</t>
-        </is>
-      </c>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
-      <c r="H23" s="5"/>
-      <c r="I23" s="5"/>
-      <c r="J23" s="5"/>
-      <c r="K23" s="5"/>
-    </row>
-    <row r="24" spans="1:11" ht="138.70272827148438" customHeight="1"/>
-    <row r="26" spans="1:11" ht="24" customHeight="1">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4. Notepad output - TC 3</t>
-        </is>
-      </c>
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
-      <c r="F26" s="5"/>
-      <c r="G26" s="5"/>
-      <c r="H26" s="5"/>
-      <c r="I26" s="5"/>
-      <c r="J26" s="5"/>
-      <c r="K26" s="5"/>
-    </row>
-    <row r="27" spans="1:11" ht="165.6273193359375" customHeight="1"/>
+      <c r="L13" s="1"/>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="3">
     <mergeCell ref="A3:C3"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="B15:K15"/>
-    <mergeCell ref="B17:K17"/>
-    <mergeCell ref="B20:K20"/>
-    <mergeCell ref="B23:K23"/>
-    <mergeCell ref="B26:K26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
